--- a/data/trans_orig/IP31KM09_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM09_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>112734</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>107112</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>116355</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>93,01%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>88,37%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>98063</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>93839</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>100246</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>92,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>125962</t>
+          <t>96856</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119532</t>
+          <t>93051</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>130363</t>
+          <t>99004</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>224026</t>
+          <t>209590</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>216023</t>
+          <t>203087</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>228671</t>
+          <t>214396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8475</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4854</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14097</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3646</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1463</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7870</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>11968</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>18471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86781</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>81971</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>88812</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>96,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>91,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>84044</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>77761</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>88193</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>83,26%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>94,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90050</t>
+          <t>86055</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84267</t>
+          <t>80103</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92338</t>
+          <t>90197</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>174094</t>
+          <t>172836</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167086</t>
+          <t>165534</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>179152</t>
+          <t>177826</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3099</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1068</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7909</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9348</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5199</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15631</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>15307</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>13007</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>54700</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>51406</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>97,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>92,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>47123</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>43715</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>48999</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>87,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61002</t>
+          <t>49110</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58187</t>
+          <t>44879</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>50900</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>108124</t>
+          <t>103810</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103251</t>
+          <t>99984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110628</t>
+          <t>106091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1144</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4438</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2966</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1090</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6374</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9171</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>184135</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>176181</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>189760</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>89,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>96,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>204042</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>196671</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>209272</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>94,67%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>199062</t>
+          <t>165384</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>191324</t>
+          <t>159503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>205312</t>
+          <t>169890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>403105</t>
+          <t>349518</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>392824</t>
+          <t>339152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>411031</t>
+          <t>357305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13178</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7553</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21132</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>11495</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6265</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18866</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>25091</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17165</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35372</t>
+          <t>34801</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>127417</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>101257</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>137597</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>94,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>104122</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>98398</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>108758</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>90,14%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>85,19%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>137890</t>
+          <t>104409</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102203</t>
+          <t>98647</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150228</t>
+          <t>108674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>231826</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>202918</t>
+          <t>198558</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>254486</t>
+          <t>242362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18169</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7989</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>44329</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>30,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>11387</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>6751</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>17111</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9233</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57258</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>32958</t>
+          <t>29226</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20484</t>
+          <t>18690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72052</t>
+          <t>62494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>61987</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>57475</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>64317</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>87,26%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>62499</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>56508</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>65737</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>82,02%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>65276</t>
+          <t>63794</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60987</t>
+          <t>58278</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67697</t>
+          <t>67400</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>127774</t>
+          <t>125782</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>121709</t>
+          <t>119090</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131955</t>
+          <t>130248</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3876</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1546</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8388</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>12,74%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>6396</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3158</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>12387</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>17,98%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>10151</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16216</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>627754</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>598363</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>641425</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>88,56%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>94,93%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>832</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>599893</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>587187</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>609379</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>92,99%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>91,02%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>679242</t>
+          <t>565608</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>635581</t>
+          <t>554235</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>694082</t>
+          <t>575051</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1279135</t>
+          <t>1193363</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1237294</t>
+          <t>1164107</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1298228</t>
+          <t>1210315</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>47941</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>34270</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>77332</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>11,44%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>45238</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>35752</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>57944</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>53126</t>
+          <t>44624</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38286</t>
+          <t>35181</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>96787</t>
+          <t>55997</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>98364</t>
+          <t>92564</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>79271</t>
+          <t>75612</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>140205</t>
+          <t>121820</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
